--- a/history/nbv_history_DPEN_False.xlsx
+++ b/history/nbv_history_DPEN_False.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,84 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>163.3440428380187</v>
+        <v>164.0060240963855</v>
       </c>
       <c r="C5" t="n">
         <v>3.601728103301022</v>
       </c>
       <c r="D5" t="n">
-        <v>5146.699081584154</v>
+        <v>5147.36106284252</v>
       </c>
       <c r="E5" t="n">
         <v>10.77532486487088</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>34.45950920245399</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4.060093689808553</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5181.158590786607</v>
-      </c>
-      <c r="E6" t="n">
-        <v>14.83541855467943</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>10.45858343337335</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.776250684600271</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5191.61717421998</v>
-      </c>
-      <c r="E7" t="n">
-        <v>18.6116692392797</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>6.006250000000001</v>
-      </c>
-      <c r="C8" t="n">
-        <v>5.121342853322978</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5197.623424219981</v>
-      </c>
-      <c r="E8" t="n">
-        <v>23.73301209260268</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1.83499122293739</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.37351493843762</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5199.458415442919</v>
-      </c>
-      <c r="E9" t="n">
-        <v>25.1065270310403</v>
       </c>
     </row>
   </sheetData>
